--- a/sample-data/sample-run/output/Tech Review.xlsx
+++ b/sample-data/sample-run/output/Tech Review.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>'Incurred Loss' most recent period has highest IBNR%</t>
+          <t>'Incurred Loss' IBNR% non-increasing as maturity increases</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Most recent=32.3%, max=40.2%</t>
+          <t>3 reversal(s) (within N/5=4 tolerance)</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>'Incurred Loss' IBNR% non-increasing as maturity increases</t>
+          <t>'Paid Loss' IBNR% non-increasing as maturity increases</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -564,12 +564,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>'Paid Loss' IBNR% non-increasing as maturity increases</t>
+          <t>'Reported Count' selections near-integer</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>4 reversal(s) (within N/5=4 tolerance)</t>
+          <t>17 period(s) with fractional selected count &gt; 0.5</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Slight negatives (within tolerance) periods: ['2005', '2006', '2007', '2012', '2014', '2017', '2022']</t>
+          <t>Slight negatives (within tolerance) periods: ['2001', '2002', '2006', '2008', '2009', '2013', '2014', '2015', '2017', '2018', '2020', '2021']</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>11 reversal(s) (exceeds N/5=4 tolerance)</t>
+          <t>9 reversal(s) (exceeds N/5=4 tolerance)</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Violations: ['2003', '2005', '2007', '2010', '2013', '2014', '2017', '2020', '2021'] (review if expected)</t>
+          <t>Violations: ['2017', '2021', '2022', '2023'] (review if expected)</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>8 cell(s) &gt; 1.0</t>
+          <t>1 cell(s) &gt; 1.0</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>98 cell(s) &gt; 1.0</t>
+          <t>20 cell(s) &gt; 1.0</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>70 cell(s) where Inc &lt; Paid</t>
+          <t>183 cell(s) where Inc &lt; Paid</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>8 cell(s) &lt; 0</t>
+          <t>1 cell(s) &lt; 0</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>82 cell(s) where Unpaid &lt; IBNR</t>
+          <t>207 cell(s) where Unpaid &lt; IBNR</t>
         </is>
       </c>
     </row>
@@ -1087,17 +1087,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>12. Paid-to-Incurred Raw Data</t>
+          <t>11. Development Factors</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Paid/Incurred ratio non-decreasing with maturity</t>
+          <t>'CL - Exposure' development factors</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4 reversal(s)</t>
+          <t>No triangle data</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>13. Case Reserve Reasonableness</t>
+          <t>12. Paid-to-Incurred Raw Data</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Case reserve % of incurred non-increasing with maturity</t>
+          <t>Paid/Incurred ratio non-decreasing with maturity</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1131,17 +1131,17 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>14. Closure Rate Checks</t>
+          <t>13. Case Reserve Reasonableness</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Closure rate checks</t>
+          <t>Case reserve % of incurred non-increasing with maturity</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Reported Count and/or Closed Count missing — skipping</t>
+          <t>4 reversal(s)</t>
         </is>
       </c>
     </row>
@@ -1153,17 +1153,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>15. Severity / Frequency Trends</t>
+          <t>14. Closure Rate Checks</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>YoY severity change &gt; 25% detected</t>
+          <t>Closure rate checks</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>14 period(s): ['period 3: 45%', 'period 4: 100%', 'period 6: 228%']</t>
+          <t>Reported Count and/or Closed Count missing — skipping</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,56 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
+          <t>YoY severity change &gt; 25% detected</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>13 period(s): ['period 3: 45%', 'period 4: 102%', 'period 6: 231%']</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>15. Severity / Frequency Trends</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
           <t>Frequency spike &gt; 2x median detected</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>5 period(s) above 2x median (0.0000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>16. Selection Reasonableness</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>'Paid Loss' selections within range of method indications</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>1 period(s): ['2010: sel=1,358,891 outside [1,134,301, 1,350,189]']</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D127"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1249,7 +1293,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>23 sheets</t>
+          <t>24 sheets</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1609,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>3. Current Age / Maturity</t>
+          <t>2. Period Consistency</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>All current ages &gt; 0</t>
+          <t>'CL - Exposure' contains all expected periods</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr"/>
@@ -1588,14 +1632,10 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>All current ages multiples of 12</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>11-month development pattern detected (ages 11, 23, 35, ...) — valid</t>
-        </is>
-      </c>
+          <t>All current ages &gt; 0</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1610,12 +1650,12 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Max current age within range</t>
+          <t>All current ages multiples of 12</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>11-month development pattern detected (ages 11, 23, 35, ...) — valid</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1672,12 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Min current age &gt;= 11</t>
+          <t>Max current age within range</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>287</t>
         </is>
       </c>
     </row>
@@ -1654,10 +1694,14 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Current age decreases as period increases (older = more mature)</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr"/>
+          <t>Min current age &gt;= 11</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1667,12 +1711,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>4. Selected Ultimate Integrity</t>
+          <t>3. Current Age / Maturity</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>'Incurred Loss' no null Selected Ultimates</t>
+          <t>Current age decreases as period increases (older = more mature)</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr"/>
@@ -1690,7 +1734,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>'Incurred Loss' all Selected Ultimates &gt; 0</t>
+          <t>'Incurred Loss' no null Selected Ultimates</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr"/>
@@ -1708,7 +1752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>'Incurred Loss' IBNR = Selected - Actual (arithmetic)</t>
+          <t>'Incurred Loss' all Selected Ultimates &gt; 0</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr"/>
@@ -1726,7 +1770,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>'Incurred Loss' IBNR &gt;= 0</t>
+          <t>'Incurred Loss' IBNR = Selected - Actual (arithmetic)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr"/>
@@ -1744,7 +1788,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>'Incurred Loss' Chain Ladder &gt;= Actual</t>
+          <t>'Incurred Loss' IBNR &gt;= 0</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr"/>
@@ -1762,72 +1806,72 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
+          <t>'Incurred Loss' Chain Ladder &gt;= Actual</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
           <t>'Incurred Loss' BF &gt;= Actual</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>'Incurred Loss' most recent period has highest IBNR%</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Most recent=32.3%, max=40.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>45.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>'Incurred Loss' IBNR% non-increasing as maturity increases</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>7 reversal(s) (exceeds N/5=4 tolerance)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>4. Selected Ultimate Integrity</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>'Incurred Loss' no extreme outlier ultimates</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>3 reversal(s) (within N/5=4 tolerance)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -1842,7 +1886,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>'Incurred Loss' periods in plausible range (1990-2030)</t>
+          <t>'Incurred Loss' no extreme outlier ultimates</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr"/>
@@ -1860,7 +1904,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>'Paid Loss' no null Selected Ultimates</t>
+          <t>'Incurred Loss' periods in plausible range (1990-2030)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr"/>
@@ -1878,7 +1922,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>'Paid Loss' all Selected Ultimates &gt; 0</t>
+          <t>'Paid Loss' no null Selected Ultimates</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr"/>
@@ -1896,7 +1940,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>'Paid Loss' IBNR = Selected - Actual (arithmetic)</t>
+          <t>'Paid Loss' all Selected Ultimates &gt; 0</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr"/>
@@ -1914,7 +1958,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>'Paid Loss' IBNR &gt;= 0</t>
+          <t>'Paid Loss' IBNR = Selected - Actual (arithmetic)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr"/>
@@ -1932,7 +1976,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>'Paid Loss' Chain Ladder &gt;= Actual</t>
+          <t>'Paid Loss' IBNR &gt;= 0</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr"/>
@@ -1950,7 +1994,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>'Paid Loss' BF &gt;= Actual</t>
+          <t>'Paid Loss' Chain Ladder &gt;= Actual</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr"/>
@@ -1968,54 +2012,54 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
+          <t>'Paid Loss' BF &gt;= Actual</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
           <t>'Paid Loss' most recent period has highest IBNR%</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>72.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>73.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>'Paid Loss' IBNR% non-increasing as maturity increases</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>4 reversal(s) (within N/5=4 tolerance)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>4. Selected Ultimate Integrity</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>'Paid Loss' no extreme outlier ultimates</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>7 reversal(s) (exceeds N/5=4 tolerance)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -2030,7 +2074,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>'Paid Loss' periods in plausible range (1990-2030)</t>
+          <t>'Paid Loss' no extreme outlier ultimates</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
@@ -2048,7 +2092,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>'Reported Count' no null Selected Ultimates</t>
+          <t>'Paid Loss' periods in plausible range (1990-2030)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr"/>
@@ -2066,7 +2110,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>'Reported Count' all Selected Ultimates &gt; 0</t>
+          <t>'Reported Count' no null Selected Ultimates</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr"/>
@@ -2084,68 +2128,72 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>'Reported Count' selections near-integer (count measure)</t>
+          <t>'Reported Count' all Selected Ultimates &gt; 0</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>'Reported Count' selections near-integer</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>17 period(s) with fractional selected count &gt; 0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>'Reported Count' IBNR = Selected - Actual (arithmetic)</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>'Reported Count' IBNR &gt;= 0</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>Slight negatives (within tolerance) periods: ['2005', '2006', '2007', '2012', '2014', '2017', '2022']</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>4. Selected Ultimate Integrity</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>'Reported Count' Chain Ladder &gt;= Actual</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr"/>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Slight negatives (within tolerance) periods: ['2001', '2002', '2006', '2008', '2009', '2013', '2014', '2015', '2017', '2018', '2020', '2021']</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -2160,54 +2208,54 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
+          <t>'Reported Count' Chain Ladder &gt;= Actual</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
           <t>'Reported Count' most recent period has highest IBNR%</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>10.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>'Reported Count' IBNR% non-increasing as maturity increases</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>11 reversal(s) (exceeds N/5=4 tolerance)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>4. Selected Ultimate Integrity</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>'Reported Count' no extreme outlier ultimates</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>9 reversal(s) (exceeds N/5=4 tolerance)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -2222,7 +2270,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>'Reported Count' periods in plausible range (1990-2030)</t>
+          <t>'Reported Count' no extreme outlier ultimates</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr"/>
@@ -2235,55 +2283,55 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>'Reported Count' periods in plausible range (1990-2030)</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
           <t>5. Cross-Measure Consistency</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>Incurred Loss and Paid Loss same periods</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>5. Cross-Measure Consistency</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>Paid Loss selected &lt;= Incurred Loss selected</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Violations: ['2003', '2005', '2007', '2010', '2013', '2014', '2017', '2020', '2021'] (review if expected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>5. Cross-Measure Consistency</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Incurred Loss: Unpaid &gt;= IBNR (all periods)</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Violations: ['2017', '2021', '2022', '2023'] (review if expected)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -2293,19 +2341,15 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>6. Sel - Sheet Consistency</t>
+          <t>5. Cross-Measure Consistency</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Sel - sheets are the primary measure sheets (values file format)</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Self-comparison skipped</t>
-        </is>
-      </c>
+          <t>Incurred Loss: Unpaid &gt;= IBNR (all periods)</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -2315,105 +2359,105 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
+          <t>6. Sel - Sheet Consistency</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Sel - sheets are the primary measure sheets (values file format)</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Self-comparison skipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>'Incurred-to-Ult' row count = period count</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>'Incurred-to-Ult' all values in (0, 1]</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>8 cell(s) &gt; 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>1 cell(s) &gt; 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>'Incurred-to-Ult' most-mature diagonal ~= 1.0</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>0.9789</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>'Incurred-to-Ult' non-decreasing across ages</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>31 reversal(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>7. X-to-Ult Triangles</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>'Paid-to-Ult' row count = period count</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
     </row>
@@ -2430,10 +2474,14 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>'Paid-to-Ult' all values in (0, 1]</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr"/>
+          <t>'Paid-to-Ult' row count = period count</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -2448,122 +2496,118 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
+          <t>'Paid-to-Ult' all values in (0, 1]</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
           <t>'Paid-to-Ult' most-mature diagonal ~= 1.0</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>0.9961</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>0.9960</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>'Paid-to-Ult' non-decreasing across ages</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>5 reversal(s)</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>'Reported-to-Ult' row count = period count</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>'Reported-to-Ult' all values in (0, 1]</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>98 cell(s) &gt; 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>20 cell(s) &gt; 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>'Reported-to-Ult' most-mature diagonal ~= 1.0</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>0.9996</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>7. X-to-Ult Triangles</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>'Reported-to-Ult' non-decreasing across ages</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>6 reversal(s)</t>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>1.0000</t>
         </is>
       </c>
     </row>
@@ -2580,12 +2624,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Incurred-to-Ult &gt;= Paid-to-Ult</t>
+          <t>'Reported-to-Ult' non-decreasing across ages</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>70 cell(s) where Inc &lt; Paid</t>
+          <t>6 reversal(s)</t>
         </is>
       </c>
     </row>
@@ -2597,17 +2641,17 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>8. Average IBNR / Unpaid</t>
+          <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Average IBNR all values &gt;= 0</t>
+          <t>Incurred-to-Ult &gt;= Paid-to-Ult</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>8 cell(s) &lt; 0</t>
+          <t>183 cell(s) where Inc &lt; Paid</t>
         </is>
       </c>
     </row>
@@ -2624,34 +2668,34 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
+          <t>Average IBNR all values &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>1 cell(s) &lt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
           <t>Average IBNR non-increasing across ages</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>31 reversal(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>8. Average IBNR / Unpaid</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>Average IBNR most-mature period final value ~= 0</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2668,94 +2712,98 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
+          <t>Average IBNR most-mature period final value ~= 0</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>68,337</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
           <t>Average Unpaid all values &gt;= 0</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>8. Average IBNR / Unpaid</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>Average Unpaid non-increasing across ages</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>5 reversal(s)</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>8. Average IBNR / Unpaid</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>Average Unpaid most-mature period final value ~= 0</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>11,865</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>12,077</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>8. Average IBNR / Unpaid</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>Average Unpaid &gt;= Average IBNR</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>82 cell(s) where Unpaid &lt; IBNR</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>9. Diagnostics</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>Ultimate Severity &gt; 0 for all periods</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr"/>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>207 cell(s) where Unpaid &lt; IBNR</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -2770,14 +2818,10 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Ultimate Severity no outliers</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Median=4,594</t>
-        </is>
-      </c>
+          <t>Ultimate Severity &gt; 0 for all periods</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -2792,12 +2836,12 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>Loss Rate in (0, 2.0)</t>
+          <t>Ultimate Severity no outliers</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Range: 0.002-0.014</t>
+          <t>Median=4,614</t>
         </is>
       </c>
     </row>
@@ -2814,10 +2858,14 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Ultimate Frequency &gt; 0 for all periods</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="inlineStr"/>
+          <t>Loss Rate in (0, 2.0)</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Range: 0.002-0.014</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -2827,55 +2875,55 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
+          <t>9. Diagnostics</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Ultimate Frequency &gt; 0 for all periods</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>'CL - Incurred Loss' diagonal = Actual in measure sheet</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>'CL - Incurred Loss' non-decreasing across ages</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>31 reversal(s)</t>
         </is>
       </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>10. CL Triangle Integrity</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>'CL - Incurred Loss' no negative values</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -2890,7 +2938,7 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>'CL - Incurred Loss' age headers are positive integers</t>
+          <t>'CL - Incurred Loss' no negative values</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr"/>
@@ -2908,50 +2956,50 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
+          <t>'CL - Incurred Loss' age headers are positive integers</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
           <t>'CL - Paid Loss' diagonal = Actual in measure sheet</t>
         </is>
       </c>
-      <c r="D86" s="7" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>'CL - Paid Loss' non-decreasing across ages</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>5 reversal(s)</t>
         </is>
       </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>10. CL Triangle Integrity</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>'CL - Paid Loss' no negative values</t>
-        </is>
-      </c>
-      <c r="D88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -2966,7 +3014,7 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>'CL - Paid Loss' age headers are positive integers</t>
+          <t>'CL - Paid Loss' no negative values</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr"/>
@@ -2984,50 +3032,50 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
+          <t>'CL - Paid Loss' age headers are positive integers</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
           <t>'CL - Reported Count' diagonal = Actual in measure sheet</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>'CL - Reported Count' non-decreasing across ages</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>6 reversal(s)</t>
         </is>
       </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>10. CL Triangle Integrity</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>'CL - Reported Count' no negative values</t>
-        </is>
-      </c>
-      <c r="D92" s="7" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -3042,7 +3090,7 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>'CL - Reported Count' age headers are positive integers</t>
+          <t>'CL - Reported Count' no negative values</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr"/>
@@ -3060,7 +3108,7 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>'CL - Diag - Rptd Claims' non-decreasing across ages</t>
+          <t>'CL - Reported Count' age headers are positive integers</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr"/>
@@ -3078,7 +3126,7 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>'CL - Diag - Rptd Claims' age headers are positive integers</t>
+          <t>'CL - Exposure' non-decreasing across ages</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr"/>
@@ -3096,7 +3144,7 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>'CL - Diag - Inc Severity' non-decreasing across ages</t>
+          <t>'CL - Exposure' age headers are positive integers</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr"/>
@@ -3114,7 +3162,7 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>'CL - Diag - Inc Severity' age headers are positive integers</t>
+          <t>'CL - Diag - Rptd Claims' non-decreasing across ages</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr"/>
@@ -3132,7 +3180,7 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>'CL - Diag - Paid to Incurred' non-decreasing across ages</t>
+          <t>'CL - Diag - Rptd Claims' age headers are positive integers</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr"/>
@@ -3150,7 +3198,7 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>'CL - Diag - Paid to Incurred' age headers are positive integers</t>
+          <t>'CL - Diag - Inc Severity' non-decreasing across ages</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr"/>
@@ -3168,7 +3216,7 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>'CL - Diag - Incr Inc Svty' non-decreasing across ages</t>
+          <t>'CL - Diag - Inc Severity' age headers are positive integers</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr"/>
@@ -3186,7 +3234,7 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>'CL - Diag - Incr Inc Svty' age headers are positive integers</t>
+          <t>'CL - Diag - Paid to Incurred' non-decreasing across ages</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr"/>
@@ -3204,7 +3252,7 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>'CL - Incurred Loss - CV &amp; Slope' non-decreasing across ages</t>
+          <t>'CL - Diag - Paid to Incurred' age headers are positive integers</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr"/>
@@ -3222,7 +3270,7 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>'CL - Paid Loss - CV &amp; Slopes' non-decreasing across ages</t>
+          <t>'CL - Diag - Incr Inc Svty' non-decreasing across ages</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr"/>
@@ -3240,76 +3288,64 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
+          <t>'CL - Diag - Incr Inc Svty' age headers are positive integers</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>'CL - Incurred Loss - CV &amp; Slope' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>'CL - Paid Loss - CV &amp; Slopes' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
           <t>'CL - Reported Count - CV &amp; Slop' non-decreasing across ages</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>11. Development Factors</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>'CL - Incurred Loss' link ratios within ceilings</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>96 violation(s): ['2001 11-&gt;23: 2.740 (ceil 1.05)', '2002 11-&gt;23: 1.430 (ceil 1.05)']</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>11. Development Factors</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>'CL - Incurred Loss' link ratios &gt;= 1.0</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>31 below 1.0: ['2006 23-&gt;35: 0.8692', '2009 23-&gt;35: 0.9424']</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>11. Development Factors</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>'CL - Incurred Loss' average LDFs non-increasing with age</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>4 reversal(s) (younger age avg &lt; older age avg)</t>
-        </is>
-      </c>
+      <c r="D107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -3324,12 +3360,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>'CL - Paid Loss' link ratios within ceilings</t>
+          <t>'CL - Incurred Loss' link ratios within ceilings</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>107 violation(s): ['2001 11-&gt;23: 3.212 (ceil 1.05)', '2002 11-&gt;23: 2.549 (ceil 1.05)']</t>
+          <t>96 violation(s): ['2001 11-&gt;23: 2.740 (ceil 1.05)', '2002 11-&gt;23: 1.430 (ceil 1.05)']</t>
         </is>
       </c>
     </row>
@@ -3346,32 +3382,36 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>'CL - Paid Loss' link ratios &gt;= 1.0</t>
+          <t>'CL - Incurred Loss' link ratios &gt;= 1.0</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>5 below 1.0: ['2013 59-&gt;71: 0.9974', '2001 71-&gt;83: 0.9904']</t>
+          <t>31 below 1.0: ['2006 23-&gt;35: 0.8692', '2009 23-&gt;35: 0.9424']</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>'CL - Paid Loss' average LDFs non-increasing with age</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="inlineStr"/>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>'CL - Incurred Loss' average LDFs non-increasing with age</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>4 reversal(s) (younger age avg &lt; older age avg)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -3386,12 +3426,12 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>'CL - Reported Count' link ratios within ceilings</t>
+          <t>'CL - Paid Loss' link ratios within ceilings</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>12 violation(s): ['2001 11-&gt;23: 1.070 (ceil 1.05)', '2004 11-&gt;23: 1.059 (ceil 1.05)']</t>
+          <t>107 violation(s): ['2001 11-&gt;23: 3.212 (ceil 1.05)', '2002 11-&gt;23: 2.549 (ceil 1.05)']</t>
         </is>
       </c>
     </row>
@@ -3408,12 +3448,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>'CL - Reported Count' link ratios &gt;= 1.0</t>
+          <t>'CL - Paid Loss' link ratios &gt;= 1.0</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>6 below 1.0: ['2005 35-&gt;47: 0.9979', '2003 47-&gt;59: 0.9952']</t>
+          <t>5 below 1.0: ['2013 59-&gt;71: 0.9974', '2001 71-&gt;83: 0.9904']</t>
         </is>
       </c>
     </row>
@@ -3430,28 +3470,32 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>'CL - Reported Count' average LDFs non-increasing with age</t>
+          <t>'CL - Paid Loss' average LDFs non-increasing with age</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>12. Paid-to-Incurred Raw Data</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>Paid Actual &lt;= Incurred Actual for all periods</t>
-        </is>
-      </c>
-      <c r="D114" s="7" t="inlineStr"/>
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>'CL - Reported Count' link ratios within ceilings</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>12 violation(s): ['2001 11-&gt;23: 1.070 (ceil 1.05)', '2004 11-&gt;23: 1.059 (ceil 1.05)']</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -3461,17 +3505,17 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>12. Paid-to-Incurred Raw Data</t>
+          <t>11. Development Factors</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Paid/Incurred ratio non-decreasing with maturity</t>
+          <t>'CL - Reported Count' link ratios &gt;= 1.0</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>4 reversal(s)</t>
+          <t>6 below 1.0: ['2005 35-&gt;47: 0.9979', '2003 47-&gt;59: 0.9952']</t>
         </is>
       </c>
     </row>
@@ -3483,119 +3527,115 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>'CL - Reported Count' average LDFs non-increasing with age</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>'CL - Exposure' development factors</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>No triangle data</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
           <t>12. Paid-to-Incurred Raw Data</t>
         </is>
       </c>
-      <c r="C116" s="6" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>Paid Actual &lt;= Incurred Actual for all periods</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>12. Paid-to-Incurred Raw Data</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Paid/Incurred ratio non-decreasing with maturity</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>4 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>12. Paid-to-Incurred Raw Data</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>Paid &lt;= Incurred at all CL triangle cells</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
+      <c r="D120" s="7" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
         <is>
           <t>13. Case Reserve Reasonableness</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr">
+      <c r="C121" s="6" t="inlineStr">
         <is>
           <t>Case reserves (Incurred - Paid Actual) &gt;= 0 for all periods</t>
         </is>
       </c>
-      <c r="D117" s="7" t="inlineStr">
+      <c r="D121" s="7" t="inlineStr">
         <is>
           <t>Min: 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>13. Case Reserve Reasonableness</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>Case reserve % of incurred non-increasing with maturity</t>
-        </is>
-      </c>
-      <c r="D118" s="4" t="inlineStr">
-        <is>
-          <t>4 reversal(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>13. Case Reserve Reasonableness</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>Unpaid - IBNR = Incurred - Paid Actual (identity)</t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>14. Closure Rate Checks</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>Closure rate checks</t>
-        </is>
-      </c>
-      <c r="D120" s="4" t="inlineStr">
-        <is>
-          <t>Reported Count and/or Closed Count missing — skipping</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>15. Severity / Frequency Trends</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>YoY severity change &gt; 25% detected</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>14 period(s): ['period 3: 45%', 'period 4: 100%', 'period 6: 228%']</t>
         </is>
       </c>
     </row>
@@ -3607,17 +3647,17 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>15. Severity / Frequency Trends</t>
+          <t>13. Case Reserve Reasonableness</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Frequency spike &gt; 2x median detected</t>
+          <t>Case reserve % of incurred non-increasing with maturity</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>5 period(s) above 2x median (0.0000)</t>
+          <t>4 reversal(s)</t>
         </is>
       </c>
     </row>
@@ -3629,75 +3669,79 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>16. Selection Reasonableness</t>
+          <t>13. Case Reserve Reasonableness</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>'Incurred Loss' selections within range of method indications</t>
+          <t>Unpaid - IBNR = Incurred - Paid Actual (identity)</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>16. Selection Reasonableness</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>'Incurred Loss' selections show method differentiation</t>
-        </is>
-      </c>
-      <c r="D124" s="7" t="inlineStr">
-        <is>
-          <t>3/24 periods = CL</t>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>14. Closure Rate Checks</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Closure rate checks</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>Reported Count and/or Closed Count missing — skipping</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>16. Selection Reasonableness</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>'Paid Loss' selections within range of method indications</t>
-        </is>
-      </c>
-      <c r="D125" s="7" t="inlineStr"/>
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>15. Severity / Frequency Trends</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>YoY severity change &gt; 25% detected</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>13 period(s): ['period 3: 45%', 'period 4: 102%', 'period 6: 231%']</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>16. Selection Reasonableness</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>'Paid Loss' selections show method differentiation</t>
-        </is>
-      </c>
-      <c r="D126" s="7" t="inlineStr">
-        <is>
-          <t>10/24 periods = CL</t>
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>15. Severity / Frequency Trends</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Frequency spike &gt; 2x median detected</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>5 period(s) above 2x median (0.0000)</t>
         </is>
       </c>
     </row>
@@ -3714,10 +3758,94 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
+          <t>'Incurred Loss' selections within range of method indications</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>16. Selection Reasonableness</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' selections show method differentiation</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>18/24 periods = CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>16. Selection Reasonableness</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>'Paid Loss' selections within range of method indications</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>1 period(s): ['2010: sel=1,358,891 outside [1,134,301, 1,350,189]']</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>16. Selection Reasonableness</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>'Paid Loss' selections show method differentiation</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>0/24 periods = CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>16. Selection Reasonableness</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
           <t>'Reported Count' selections equal to Chain Ladder (only available method)</t>
         </is>
       </c>
-      <c r="D127" s="7" t="inlineStr">
+      <c r="D131" s="7" t="inlineStr">
         <is>
           <t>No IE/BF available — CL is the sole method</t>
         </is>
